--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1038,6 +1038,980 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131783159</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58583</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>590123</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6335191</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131785691</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fagerön, Påskallavik, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>590134</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6335089</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131785005</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fagerön, Fagerön, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>590036</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6335281</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131785189</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79883</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>590053</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6335204</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131785807</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fagerön, Påskallavik, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>590134</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6335089</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131786049</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79883</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sanden, Sanden, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>590167</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6335066</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131784443</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>590105</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6335233</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131785836</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58549</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fagerön, Påskallavik, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>590134</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6335089</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131785895</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79883</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>590157</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6335054</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1384,48 +1384,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131785189</v>
+        <v>131785807</v>
       </c>
       <c r="B8" t="n">
-        <v>79883</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590053</v>
+        <v>590134</v>
       </c>
       <c r="R8" t="n">
-        <v>6335204</v>
+        <v>6335089</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,9 +1461,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,69 +1488,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131785807</v>
+        <v>131785189</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>79883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590134</v>
+        <v>590053</v>
       </c>
       <c r="R9" t="n">
-        <v>6335089</v>
+        <v>6335204</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,19 +1568,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,12 +1585,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1384,57 +1384,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131785807</v>
+        <v>131785189</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>79883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590134</v>
+        <v>590053</v>
       </c>
       <c r="R8" t="n">
-        <v>6335089</v>
+        <v>6335204</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,19 +1452,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,60 +1469,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131785189</v>
+        <v>131785807</v>
       </c>
       <c r="B9" t="n">
-        <v>79883</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590053</v>
+        <v>590134</v>
       </c>
       <c r="R9" t="n">
-        <v>6335204</v>
+        <v>6335089</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,9 +1558,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,12 +1585,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>131783159</v>
       </c>
       <c r="B5" t="n">
-        <v>58583</v>
+        <v>58585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>131785691</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>131785005</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>131785189</v>
       </c>
       <c r="B8" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>131785807</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>131786049</v>
       </c>
       <c r="B10" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>131784443</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>131785836</v>
       </c>
       <c r="B12" t="n">
-        <v>58549</v>
+        <v>58551</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>131785895</v>
       </c>
       <c r="B13" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1704,27 +1704,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131784443</v>
+        <v>131785836</v>
       </c>
       <c r="B11" t="n">
-        <v>57901</v>
+        <v>58551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1732,20 +1732,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590105</v>
+        <v>590134</v>
       </c>
       <c r="R11" t="n">
-        <v>6335233</v>
+        <v>6335089</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,9 +1781,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,39 +1808,39 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131785836</v>
+        <v>131784443</v>
       </c>
       <c r="B12" t="n">
-        <v>58551</v>
+        <v>57901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1829,29 +1848,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590134</v>
+        <v>590105</v>
       </c>
       <c r="R12" t="n">
-        <v>6335089</v>
+        <v>6335233</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,19 +1888,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,12 +1905,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1704,27 +1704,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131785836</v>
+        <v>131784443</v>
       </c>
       <c r="B11" t="n">
-        <v>58551</v>
+        <v>57901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1732,29 +1732,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590134</v>
+        <v>590105</v>
       </c>
       <c r="R11" t="n">
-        <v>6335089</v>
+        <v>6335233</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,19 +1772,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,39 +1789,39 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131784443</v>
+        <v>131785836</v>
       </c>
       <c r="B12" t="n">
-        <v>57901</v>
+        <v>58551</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1848,20 +1829,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590105</v>
+        <v>590134</v>
       </c>
       <c r="R12" t="n">
-        <v>6335233</v>
+        <v>6335089</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,9 +1878,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,12 +1905,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1384,48 +1384,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131785189</v>
+        <v>131785807</v>
       </c>
       <c r="B8" t="n">
-        <v>79885</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590053</v>
+        <v>590134</v>
       </c>
       <c r="R8" t="n">
-        <v>6335204</v>
+        <v>6335089</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,9 +1461,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,69 +1488,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131785807</v>
+        <v>131785189</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>79885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590134</v>
+        <v>590053</v>
       </c>
       <c r="R9" t="n">
-        <v>6335089</v>
+        <v>6335204</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,19 +1568,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,12 +1585,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1704,27 +1704,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131784443</v>
+        <v>131785836</v>
       </c>
       <c r="B11" t="n">
-        <v>57901</v>
+        <v>58551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1732,20 +1732,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590105</v>
+        <v>590134</v>
       </c>
       <c r="R11" t="n">
-        <v>6335233</v>
+        <v>6335089</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,9 +1781,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,39 +1808,39 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131785836</v>
+        <v>131784443</v>
       </c>
       <c r="B12" t="n">
-        <v>58551</v>
+        <v>57901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1829,29 +1848,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590134</v>
+        <v>590105</v>
       </c>
       <c r="R12" t="n">
-        <v>6335089</v>
+        <v>6335233</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,19 +1888,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,12 +1905,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1384,57 +1384,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131785807</v>
+        <v>131785189</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>79885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590134</v>
+        <v>590053</v>
       </c>
       <c r="R8" t="n">
-        <v>6335089</v>
+        <v>6335204</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,19 +1452,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,60 +1469,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131785189</v>
+        <v>131785807</v>
       </c>
       <c r="B9" t="n">
-        <v>79885</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590053</v>
+        <v>590134</v>
       </c>
       <c r="R9" t="n">
-        <v>6335204</v>
+        <v>6335089</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,9 +1558,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,12 +1585,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1704,27 +1704,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131785836</v>
+        <v>131784443</v>
       </c>
       <c r="B11" t="n">
-        <v>58551</v>
+        <v>57901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1732,29 +1732,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590134</v>
+        <v>590105</v>
       </c>
       <c r="R11" t="n">
-        <v>6335089</v>
+        <v>6335233</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,19 +1772,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,39 +1789,39 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131784443</v>
+        <v>131785836</v>
       </c>
       <c r="B12" t="n">
-        <v>57901</v>
+        <v>58551</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1848,20 +1829,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590105</v>
+        <v>590134</v>
       </c>
       <c r="R12" t="n">
-        <v>6335233</v>
+        <v>6335089</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,9 +1878,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,12 +1905,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>131783159</v>
       </c>
       <c r="B5" t="n">
-        <v>58585</v>
+        <v>58588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>131785691</v>
       </c>
       <c r="B6" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>131785005</v>
       </c>
       <c r="B7" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>131785189</v>
       </c>
       <c r="B8" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>131785807</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>131786049</v>
       </c>
       <c r="B10" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>131784443</v>
       </c>
       <c r="B11" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>131785836</v>
       </c>
       <c r="B12" t="n">
-        <v>58551</v>
+        <v>58554</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>131785895</v>
       </c>
       <c r="B13" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>131783159</v>
       </c>
       <c r="B5" t="n">
-        <v>58588</v>
+        <v>58593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>131785691</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>131785005</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,48 +1384,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131785189</v>
+        <v>131785807</v>
       </c>
       <c r="B8" t="n">
-        <v>79888</v>
+        <v>57906</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590053</v>
+        <v>590134</v>
       </c>
       <c r="R8" t="n">
-        <v>6335204</v>
+        <v>6335089</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,9 +1461,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,69 +1488,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131785807</v>
+        <v>131785189</v>
       </c>
       <c r="B9" t="n">
-        <v>57901</v>
+        <v>79893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590134</v>
+        <v>590053</v>
       </c>
       <c r="R9" t="n">
-        <v>6335089</v>
+        <v>6335204</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,19 +1568,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,12 +1585,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
         <v>131786049</v>
       </c>
       <c r="B10" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>131784443</v>
       </c>
       <c r="B11" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>131785836</v>
       </c>
       <c r="B12" t="n">
-        <v>58554</v>
+        <v>58559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>131785895</v>
       </c>
       <c r="B13" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,7 +1043,7 @@
         <v>131783159</v>
       </c>
       <c r="B5" t="n">
-        <v>58593</v>
+        <v>58595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>131785691</v>
       </c>
       <c r="B6" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>131785005</v>
       </c>
       <c r="B7" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,57 +1384,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131785807</v>
+        <v>131785189</v>
       </c>
       <c r="B8" t="n">
-        <v>57906</v>
+        <v>79895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590134</v>
+        <v>590053</v>
       </c>
       <c r="R8" t="n">
-        <v>6335089</v>
+        <v>6335204</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,19 +1452,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,60 +1469,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131785189</v>
+        <v>131785807</v>
       </c>
       <c r="B9" t="n">
-        <v>79893</v>
+        <v>57908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590053</v>
+        <v>590134</v>
       </c>
       <c r="R9" t="n">
-        <v>6335204</v>
+        <v>6335089</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,9 +1558,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,12 +1585,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
         <v>131786049</v>
       </c>
       <c r="B10" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>131784443</v>
       </c>
       <c r="B11" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>131785836</v>
       </c>
       <c r="B12" t="n">
-        <v>58559</v>
+        <v>58561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>131785895</v>
       </c>
       <c r="B13" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,6 +2011,103 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132168851</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58044</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fagerön, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>589961</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6335258</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1704,27 +1704,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131784443</v>
+        <v>131785836</v>
       </c>
       <c r="B11" t="n">
-        <v>57911</v>
+        <v>58561</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1732,20 +1732,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590105</v>
+        <v>590134</v>
       </c>
       <c r="R11" t="n">
-        <v>6335233</v>
+        <v>6335089</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,9 +1781,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,39 +1808,39 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131785836</v>
+        <v>131784443</v>
       </c>
       <c r="B12" t="n">
-        <v>58561</v>
+        <v>57911</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1829,29 +1848,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590134</v>
+        <v>590105</v>
       </c>
       <c r="R12" t="n">
-        <v>6335089</v>
+        <v>6335233</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,19 +1888,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,12 +1905,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1704,27 +1704,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131785836</v>
+        <v>131784443</v>
       </c>
       <c r="B11" t="n">
-        <v>58561</v>
+        <v>57911</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1732,29 +1732,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590134</v>
+        <v>590105</v>
       </c>
       <c r="R11" t="n">
-        <v>6335089</v>
+        <v>6335233</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,19 +1772,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,39 +1789,39 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131784443</v>
+        <v>131785836</v>
       </c>
       <c r="B12" t="n">
-        <v>57911</v>
+        <v>58561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1848,20 +1829,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590105</v>
+        <v>590134</v>
       </c>
       <c r="R12" t="n">
-        <v>6335233</v>
+        <v>6335089</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,9 +1878,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,12 +1905,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>131783159</v>
       </c>
       <c r="B5" t="n">
-        <v>58595</v>
+        <v>58629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>131785691</v>
       </c>
       <c r="B6" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>131785005</v>
       </c>
       <c r="B7" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>131785189</v>
       </c>
       <c r="B8" t="n">
-        <v>79895</v>
+        <v>79929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>131785807</v>
       </c>
       <c r="B9" t="n">
-        <v>57908</v>
+        <v>57942</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>131786049</v>
       </c>
       <c r="B10" t="n">
-        <v>79895</v>
+        <v>79929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>131784443</v>
       </c>
       <c r="B11" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>131785836</v>
       </c>
       <c r="B12" t="n">
-        <v>58561</v>
+        <v>58595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>131785895</v>
       </c>
       <c r="B13" t="n">
-        <v>79895</v>
+        <v>79929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>132168851</v>
       </c>
       <c r="B14" t="n">
-        <v>58044</v>
+        <v>58078</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>131783159</v>
       </c>
       <c r="B5" t="n">
-        <v>58629</v>
+        <v>58631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>131785189</v>
       </c>
       <c r="B8" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>131786049</v>
       </c>
       <c r="B10" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,27 +1704,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131785836</v>
+        <v>131784443</v>
       </c>
       <c r="B11" t="n">
-        <v>58595</v>
+        <v>57945</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1732,29 +1732,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590134</v>
+        <v>590105</v>
       </c>
       <c r="R11" t="n">
-        <v>6335089</v>
+        <v>6335233</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,19 +1772,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,39 +1789,39 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131784443</v>
+        <v>131785836</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>58597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1848,20 +1829,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590105</v>
+        <v>590134</v>
       </c>
       <c r="R12" t="n">
-        <v>6335233</v>
+        <v>6335089</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,9 +1878,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,12 +1905,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1920,7 +1920,7 @@
         <v>131785895</v>
       </c>
       <c r="B13" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>132168851</v>
       </c>
       <c r="B14" t="n">
-        <v>58078</v>
+        <v>58080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1384,48 +1384,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131785189</v>
+        <v>131785807</v>
       </c>
       <c r="B8" t="n">
-        <v>79936</v>
+        <v>57942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590053</v>
+        <v>590134</v>
       </c>
       <c r="R8" t="n">
-        <v>6335204</v>
+        <v>6335089</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,9 +1461,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,69 +1488,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131785807</v>
+        <v>131785189</v>
       </c>
       <c r="B9" t="n">
-        <v>57942</v>
+        <v>79936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590134</v>
+        <v>590053</v>
       </c>
       <c r="R9" t="n">
-        <v>6335089</v>
+        <v>6335204</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,19 +1568,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,12 +1585,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1384,57 +1384,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131785807</v>
+        <v>131785189</v>
       </c>
       <c r="B8" t="n">
-        <v>57942</v>
+        <v>79936</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590134</v>
+        <v>590053</v>
       </c>
       <c r="R8" t="n">
-        <v>6335089</v>
+        <v>6335204</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,19 +1452,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,60 +1469,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131785189</v>
+        <v>131785807</v>
       </c>
       <c r="B9" t="n">
-        <v>79936</v>
+        <v>57942</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590053</v>
+        <v>590134</v>
       </c>
       <c r="R9" t="n">
-        <v>6335204</v>
+        <v>6335089</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,9 +1558,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,12 +1585,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -1384,48 +1384,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131785189</v>
+        <v>131785807</v>
       </c>
       <c r="B8" t="n">
-        <v>79936</v>
+        <v>57942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590053</v>
+        <v>590134</v>
       </c>
       <c r="R8" t="n">
-        <v>6335204</v>
+        <v>6335089</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,9 +1461,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,69 +1488,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131785807</v>
+        <v>131785189</v>
       </c>
       <c r="B9" t="n">
-        <v>57942</v>
+        <v>79936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590134</v>
+        <v>590053</v>
       </c>
       <c r="R9" t="n">
-        <v>6335089</v>
+        <v>6335204</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,19 +1568,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,12 +1585,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1704,27 +1704,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131784443</v>
+        <v>131785836</v>
       </c>
       <c r="B11" t="n">
-        <v>57945</v>
+        <v>58597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1732,20 +1732,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fagerögrundet, Fagerögrundet, Sm</t>
+          <t>Fagerön, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590105</v>
+        <v>590134</v>
       </c>
       <c r="R11" t="n">
-        <v>6335233</v>
+        <v>6335089</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,9 +1781,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,39 +1808,39 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131785836</v>
+        <v>131784443</v>
       </c>
       <c r="B12" t="n">
-        <v>58597</v>
+        <v>57945</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1829,29 +1848,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerön, Påskallavik, Sm</t>
+          <t>Fagerögrundet, Fagerögrundet, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590134</v>
+        <v>590105</v>
       </c>
       <c r="R12" t="n">
-        <v>6335089</v>
+        <v>6335233</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,19 +1888,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,12 +1905,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -2017,7 +2017,7 @@
         <v>132168851</v>
       </c>
       <c r="B14" t="n">
-        <v>58080</v>
+        <v>58081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -2017,7 +2017,7 @@
         <v>132168851</v>
       </c>
       <c r="B14" t="n">
-        <v>58081</v>
+        <v>58085</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 10602-2026 artfynd.xlsx
+++ b/artfynd/A 10602-2026 artfynd.xlsx
@@ -2017,7 +2017,7 @@
         <v>132168851</v>
       </c>
       <c r="B14" t="n">
-        <v>58085</v>
+        <v>58086</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
